--- a/AC_2014/3-Karimnagar_8_27_Choppadandi_(SC).xlsx
+++ b/AC_2014/3-Karimnagar_8_27_Choppadandi_(SC).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,11 +111,33 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +172,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -20141,268 +20177,269 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="7" t="inlineStr">
+      <c r="A262" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B262" s="8" t="inlineStr"/>
-      <c r="C262" s="9">
+      <c r="B262" s="11" t="inlineStr"/>
+      <c r="C262" s="19">
         <f>SUM(C6:C261)</f>
         <v/>
       </c>
-      <c r="D262" s="9">
+      <c r="D262" s="19">
         <f>SUM(D6:D261)</f>
         <v/>
       </c>
-      <c r="E262" s="9">
+      <c r="E262" s="19">
         <f>SUM(E6:E261)</f>
         <v/>
       </c>
-      <c r="F262" s="9">
+      <c r="F262" s="19">
         <f>SUM(F6:F261)</f>
         <v/>
       </c>
-      <c r="G262" s="9">
+      <c r="G262" s="19">
         <f>SUM(G6:G261)</f>
         <v/>
       </c>
-      <c r="H262" s="9">
+      <c r="H262" s="19">
         <f>SUM(H6:H261)</f>
         <v/>
       </c>
-      <c r="I262" s="9">
+      <c r="I262" s="19">
         <f>SUM(I6:I261)</f>
         <v/>
       </c>
-      <c r="J262" s="9">
+      <c r="J262" s="19">
         <f>SUM(J6:J261)</f>
         <v/>
       </c>
-      <c r="K262" s="9">
+      <c r="K262" s="19">
         <f>SUM(K6:K261)</f>
         <v/>
       </c>
-      <c r="L262" s="9">
+      <c r="L262" s="19">
         <f>SUM(L6:L261)</f>
         <v/>
       </c>
-      <c r="M262" s="9">
+      <c r="M262" s="19">
         <f>SUM(M6:M261)</f>
         <v/>
       </c>
-      <c r="N262" s="9">
+      <c r="N262" s="19">
         <f>SUM(N6:N261)</f>
         <v/>
       </c>
-      <c r="O262" s="9">
+      <c r="O262" s="19">
         <f>SUM(O6:O261)</f>
         <v/>
       </c>
-      <c r="P262" s="9">
+      <c r="P262" s="19">
         <f>SUM(P6:P261)</f>
         <v/>
       </c>
-      <c r="Q262" s="9">
+      <c r="Q262" s="19">
         <f>SUM(Q6:Q261)</f>
         <v/>
       </c>
-      <c r="R262" s="9">
+      <c r="R262" s="19">
         <f>SUM(R6:R261)</f>
         <v/>
       </c>
-      <c r="S262" s="9">
+      <c r="S262" s="19">
         <f>SUM(S6:S261)</f>
         <v/>
       </c>
-      <c r="T262" s="9">
+      <c r="T262" s="19">
         <f>SUM(T6:T261)</f>
         <v/>
       </c>
-      <c r="U262" s="9">
+      <c r="U262" s="19">
         <f>SUM(U6:U261)</f>
         <v/>
       </c>
-      <c r="V262" s="9">
+      <c r="V262" s="19">
         <f>SUM(V6:V261)</f>
         <v/>
       </c>
-      <c r="W262" s="9">
+      <c r="W262" s="19">
         <f>SUM(W6:W261)</f>
         <v/>
       </c>
-      <c r="X262" s="9">
+      <c r="X262" s="19">
         <f>SUM(X6:X261)</f>
         <v/>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="10" t="inlineStr">
+      <c r="A263" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr"/>
-      <c r="C263" s="12" t="n">
+      <c r="C263" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="D263" s="12" t="n">
+      <c r="D263" s="19" t="n">
         <v>264</v>
       </c>
-      <c r="E263" s="12" t="n">
+      <c r="E263" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="F263" s="12" t="n">
+      <c r="F263" s="19" t="n">
         <v>64</v>
       </c>
-      <c r="G263" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H263" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I263" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J263" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K263" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L263" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M263" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N263" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O263" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P263" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q263" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R263" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S263" s="12" t="n">
+      <c r="G263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M263" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N263" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S263" s="19" t="n">
         <v>358</v>
       </c>
-      <c r="T263" s="12" t="n">
+      <c r="T263" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="U263" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V263" s="12" t="n">
+      <c r="U263" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V263" s="19" t="n">
         <v>394</v>
       </c>
-      <c r="W263" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X263" s="13" t="n">
+      <c r="W263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X263" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="14" t="inlineStr">
+      <c r="A264" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B264" s="15" t="inlineStr"/>
-      <c r="C264" s="16">
+      <c r="B264" s="11" t="inlineStr"/>
+      <c r="C264" s="20">
         <f>C262+C263</f>
         <v/>
       </c>
-      <c r="D264" s="16">
+      <c r="D264" s="20">
         <f>D262+D263</f>
         <v/>
       </c>
-      <c r="E264" s="16">
+      <c r="E264" s="20">
         <f>E262+E263</f>
         <v/>
       </c>
-      <c r="F264" s="16">
+      <c r="F264" s="20">
         <f>F262+F263</f>
         <v/>
       </c>
-      <c r="G264" s="16">
+      <c r="G264" s="20">
         <f>G262+G263</f>
         <v/>
       </c>
-      <c r="H264" s="16">
+      <c r="H264" s="20">
         <f>H262+H263</f>
         <v/>
       </c>
-      <c r="I264" s="16">
+      <c r="I264" s="20">
         <f>I262+I263</f>
         <v/>
       </c>
-      <c r="J264" s="16">
+      <c r="J264" s="20">
         <f>J262+J263</f>
         <v/>
       </c>
-      <c r="K264" s="16">
+      <c r="K264" s="20">
         <f>K262+K263</f>
         <v/>
       </c>
-      <c r="L264" s="16">
+      <c r="L264" s="20">
         <f>L262+L263</f>
         <v/>
       </c>
-      <c r="M264" s="16">
+      <c r="M264" s="20">
         <f>M262+M263</f>
         <v/>
       </c>
-      <c r="N264" s="16">
+      <c r="N264" s="20">
         <f>N262+N263</f>
         <v/>
       </c>
-      <c r="O264" s="16">
+      <c r="O264" s="20">
         <f>O262+O263</f>
         <v/>
       </c>
-      <c r="P264" s="16">
+      <c r="P264" s="20">
         <f>P262+P263</f>
         <v/>
       </c>
-      <c r="Q264" s="16">
+      <c r="Q264" s="20">
         <f>Q262+Q263</f>
         <v/>
       </c>
-      <c r="R264" s="16">
+      <c r="R264" s="20">
         <f>R262+R263</f>
         <v/>
       </c>
-      <c r="S264" s="16">
+      <c r="S264" s="20">
         <f>S262+S263</f>
         <v/>
       </c>
-      <c r="T264" s="16">
+      <c r="T264" s="20">
         <f>T262+T263</f>
         <v/>
       </c>
-      <c r="U264" s="16">
+      <c r="U264" s="20">
         <f>U262+U263</f>
         <v/>
       </c>
-      <c r="V264" s="16">
+      <c r="V264" s="20">
         <f>V262+V263</f>
         <v/>
       </c>
-      <c r="W264" s="16">
+      <c r="W264" s="20">
         <f>W262+W263</f>
         <v/>
       </c>
-      <c r="X264" s="17" t="n">
-        <v>0</v>
+      <c r="X264" s="20">
+        <f>X262+X263</f>
+        <v/>
       </c>
     </row>
   </sheetData>
